--- a/demo/assets/bill-of-materials.xlsx
+++ b/demo/assets/bill-of-materials.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bill of materials" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Suppliers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +17,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,22 +29,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004D5BE3"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,9 +50,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -423,40 +419,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Part no.</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Unit cost</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Ordered</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>In stock</t>
         </is>
       </c>
     </row>
@@ -474,13 +468,14 @@
       <c r="C2" t="n">
         <v>12</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+      <c r="D2" t="n">
         <v>184.5</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -491,19 +486,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Impeller, 140mm</t>
+          <t>Impeller 140mm "A" grade</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>12</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
+      <c r="D3" t="n">
         <v>96</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -520,13 +516,14 @@
       <c r="C4" t="n">
         <v>24</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
+      <c r="D4" t="n">
         <v>22.75</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -537,42 +534,84 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mounting bracket</t>
+          <t>Mounting bracket &lt;heavy&gt;</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>24</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
+      <c r="D5" t="n">
         <v>41.2</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>HCA-4400</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Fastener pack M8</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>box</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>13.9</v>
+      <c r="E5" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C7">
+        <f>SUM(C2:C5)</f>
+        <v/>
+      </c>
+      <c r="D7" t="n">
+        <v>344.45</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>46281.60416666666</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Lead time (days)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Rajkot Castings</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gujarat Seals</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
